--- a/yolo像素預測_11_batch4_重新標註.xlsx
+++ b/yolo像素預測_11_batch4_重新標註.xlsx
@@ -544,38 +544,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001_jpg.rf.4c9b567ff4deaebc95dfe818620028ba.jpg</t>
+          <t>001_jpg.rf.03a31d32c76ad0190046d85d172d47a8.jpg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.89</v>
+        <v>0.907</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8537</v>
+        <v>0.8768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9614</v>
+        <v>0.9741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9655</v>
+        <v>0.978</v>
       </c>
       <c r="G2" t="n">
-        <v>371.674</v>
+        <v>728.5599999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>464.98</v>
+        <v>894.203</v>
       </c>
       <c r="I2" t="n">
-        <v>318.49</v>
+        <v>667.729</v>
       </c>
       <c r="J2" t="n">
-        <v>52.801</v>
+        <v>99.146</v>
       </c>
       <c r="K2" t="n">
-        <v>415.596</v>
+        <v>797.3808</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -583,31 +583,31 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>365.4</v>
+        <v>731.799</v>
       </c>
       <c r="N2" t="n">
-        <v>450.968</v>
+        <v>901.937</v>
       </c>
       <c r="O2" t="n">
-        <v>331.754</v>
+        <v>664.509</v>
       </c>
       <c r="P2" t="n">
-        <v>68.45999999999999</v>
+        <v>136.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>383.9851</v>
+        <v>767.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>15.353</v>
+        <v>8.384</v>
       </c>
       <c r="S2" t="n">
-        <v>20.521</v>
+        <v>37.911</v>
       </c>
       <c r="T2" t="n">
-        <v>31.6109</v>
+        <v>29.4106</v>
       </c>
       <c r="U2" t="n">
-        <v>8.231999999999999</v>
+        <v>3.83</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -628,38 +628,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002_jpg.rf.e7a3fcb45d83e3a2dd6afbe241bd1d73.jpg</t>
+          <t>002_jpg.rf.d5faf51a853d609116b1525c27a0392f.jpg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.913</v>
+        <v>0.896</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8686</v>
+        <v>0.883</v>
       </c>
       <c r="E3" t="n">
-        <v>0.854</v>
+        <v>0.9759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8988</v>
+        <v>0.9681</v>
       </c>
       <c r="G3" t="n">
-        <v>174.949</v>
+        <v>381.789</v>
       </c>
       <c r="H3" t="n">
-        <v>608.83</v>
+        <v>1180.78</v>
       </c>
       <c r="I3" t="n">
-        <v>227.015</v>
+        <v>452.079</v>
       </c>
       <c r="J3" t="n">
-        <v>229.172</v>
+        <v>484.473</v>
       </c>
       <c r="K3" t="n">
-        <v>383.2122</v>
+        <v>699.8451</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>180.369</v>
+        <v>359.739</v>
       </c>
       <c r="N3" t="n">
-        <v>609.873</v>
+        <v>1219.747</v>
       </c>
       <c r="O3" t="n">
-        <v>245.542</v>
+        <v>490.084</v>
       </c>
       <c r="P3" t="n">
-        <v>244.214</v>
+        <v>488.427</v>
       </c>
       <c r="Q3" t="n">
-        <v>371.4222</v>
+        <v>742.8444</v>
       </c>
       <c r="R3" t="n">
-        <v>5.52</v>
+        <v>44.773</v>
       </c>
       <c r="S3" t="n">
-        <v>23.864</v>
+        <v>38.21</v>
       </c>
       <c r="T3" t="n">
-        <v>11.79</v>
+        <v>-42.9993</v>
       </c>
       <c r="U3" t="n">
-        <v>3.174</v>
+        <v>5.788</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -712,38 +712,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003_jpg.rf.1f6d62636a99328020108bb78ef3c835.jpg</t>
+          <t>003_jpg.rf.a31c078f0556f77ab30246cc2916b372.jpg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.913</v>
+        <v>0.805</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8475</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8601</v>
+        <v>0.9859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9671</v>
+        <v>0.9909</v>
       </c>
       <c r="G4" t="n">
-        <v>300.717</v>
+        <v>599.754</v>
       </c>
       <c r="H4" t="n">
-        <v>564.5410000000001</v>
+        <v>1280</v>
       </c>
       <c r="I4" t="n">
-        <v>314.624</v>
+        <v>579.991</v>
       </c>
       <c r="J4" t="n">
-        <v>110.616</v>
+        <v>184.251</v>
       </c>
       <c r="K4" t="n">
-        <v>454.1378</v>
+        <v>1095.927</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -751,31 +751,31 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>281.937</v>
+        <v>562.874</v>
       </c>
       <c r="N4" t="n">
-        <v>601.409</v>
+        <v>1202.818</v>
       </c>
       <c r="O4" t="n">
-        <v>319.179</v>
+        <v>637.357</v>
       </c>
       <c r="P4" t="n">
-        <v>122.327</v>
+        <v>244.654</v>
       </c>
       <c r="Q4" t="n">
-        <v>480.5272</v>
+        <v>961.0544</v>
       </c>
       <c r="R4" t="n">
-        <v>41.375</v>
+        <v>85.541</v>
       </c>
       <c r="S4" t="n">
-        <v>12.565</v>
+        <v>83.303</v>
       </c>
       <c r="T4" t="n">
-        <v>-26.3894</v>
+        <v>134.8727</v>
       </c>
       <c r="U4" t="n">
-        <v>5.492</v>
+        <v>14.034</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -796,38 +796,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004_jpg.rf.4013d1526ae79399b0311b45cce6dc49.jpg</t>
+          <t>004_jpg.rf.0b42a236baeb1f644b5f26d18058bdb0.jpg</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.851</v>
+        <v>0.91</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8638</v>
+        <v>0.8791</v>
       </c>
       <c r="E5" t="n">
-        <v>0.918</v>
+        <v>0.9795</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9489</v>
+        <v>0.9819</v>
       </c>
       <c r="G5" t="n">
-        <v>373.093</v>
+        <v>776.859</v>
       </c>
       <c r="H5" t="n">
-        <v>218.251</v>
+        <v>463.498</v>
       </c>
       <c r="I5" t="n">
-        <v>441.74</v>
+        <v>881.522</v>
       </c>
       <c r="J5" t="n">
-        <v>591.331</v>
+        <v>1136.836</v>
       </c>
       <c r="K5" t="n">
-        <v>379.3432</v>
+        <v>681.4239</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -835,31 +835,31 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>367.889</v>
+        <v>735.778</v>
       </c>
       <c r="N5" t="n">
-        <v>222.206</v>
+        <v>444.413</v>
       </c>
       <c r="O5" t="n">
-        <v>443.218</v>
+        <v>886.437</v>
       </c>
       <c r="P5" t="n">
-        <v>579.402</v>
+        <v>1158.803</v>
       </c>
       <c r="Q5" t="n">
-        <v>365.0521</v>
+        <v>730.1042</v>
       </c>
       <c r="R5" t="n">
-        <v>6.536</v>
+        <v>45.298</v>
       </c>
       <c r="S5" t="n">
-        <v>12.021</v>
+        <v>22.511</v>
       </c>
       <c r="T5" t="n">
-        <v>14.2911</v>
+        <v>-48.6803</v>
       </c>
       <c r="U5" t="n">
-        <v>3.915</v>
+        <v>6.668</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -880,38 +880,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005_jpg.rf.db41c76a1a0f67c029e07def41fa7e71.jpg</t>
+          <t>005_jpg.rf.8bc29d496b6fdd86b525b8ebc9b20046.jpg</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.851</v>
+        <v>0.854</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8639</v>
+        <v>0.902</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9243</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9436</v>
+        <v>0.9676</v>
       </c>
       <c r="G6" t="n">
-        <v>294.054</v>
+        <v>640.304</v>
       </c>
       <c r="H6" t="n">
-        <v>563.15</v>
+        <v>1104.281</v>
       </c>
       <c r="I6" t="n">
-        <v>235.136</v>
+        <v>488.124</v>
       </c>
       <c r="J6" t="n">
-        <v>182.359</v>
+        <v>320.397</v>
       </c>
       <c r="K6" t="n">
-        <v>385.3225</v>
+        <v>798.5186</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -919,31 +919,31 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>319.179</v>
+        <v>637.357</v>
       </c>
       <c r="N6" t="n">
-        <v>581.095</v>
+        <v>1162.189</v>
       </c>
       <c r="O6" t="n">
-        <v>247.235</v>
+        <v>493.47</v>
       </c>
       <c r="P6" t="n">
-        <v>184.963</v>
+        <v>369.927</v>
       </c>
       <c r="Q6" t="n">
-        <v>402.6114</v>
+        <v>805.2228</v>
       </c>
       <c r="R6" t="n">
-        <v>30.875</v>
+        <v>57.983</v>
       </c>
       <c r="S6" t="n">
-        <v>12.376</v>
+        <v>49.817</v>
       </c>
       <c r="T6" t="n">
-        <v>-17.2889</v>
+        <v>-6.7042</v>
       </c>
       <c r="U6" t="n">
-        <v>4.294</v>
+        <v>0.833</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -964,38 +964,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006_jpg.rf.d226f3637e96179b1db115d31f983def.jpg</t>
+          <t>006_jpg.rf.eb96c2293c79c85b54c52caffcc55e16.jpg</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.875</v>
+        <v>0.833</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8549</v>
+        <v>0.851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9509</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9736</v>
+        <v>0.9816</v>
       </c>
       <c r="G7" t="n">
-        <v>350.031</v>
+        <v>700.095</v>
       </c>
       <c r="H7" t="n">
-        <v>550.327</v>
+        <v>1167.344</v>
       </c>
       <c r="I7" t="n">
-        <v>324.055</v>
+        <v>610.732</v>
       </c>
       <c r="J7" t="n">
-        <v>124.676</v>
+        <v>159.653</v>
       </c>
       <c r="K7" t="n">
-        <v>426.4434</v>
+        <v>1011.6452</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1003,31 +1003,31 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>331.875</v>
+        <v>662.749</v>
       </c>
       <c r="N7" t="n">
-        <v>563.319</v>
+        <v>1126.639</v>
       </c>
       <c r="O7" t="n">
-        <v>314.1</v>
+        <v>627.201</v>
       </c>
       <c r="P7" t="n">
-        <v>102.859</v>
+        <v>205.718</v>
       </c>
       <c r="Q7" t="n">
-        <v>460.8032</v>
+        <v>921.6065</v>
       </c>
       <c r="R7" t="n">
-        <v>22.326</v>
+        <v>55.241</v>
       </c>
       <c r="S7" t="n">
-        <v>23.981</v>
+        <v>48.92</v>
       </c>
       <c r="T7" t="n">
-        <v>-34.3599</v>
+        <v>90.03870000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>7.457</v>
+        <v>9.77</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>007_jpg.rf.700d0bf10fa8fd648835e0074572e5d8.jpg</t>
+          <t>007_jpg.rf.e24bee6503119dbfd99ebc0061731e38.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1058,28 +1058,28 @@
         <v>0.858</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8542</v>
+        <v>0.8494</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8256</v>
+        <v>0.9751</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9568</v>
+        <v>0.8647</v>
       </c>
       <c r="G8" t="n">
-        <v>291.39</v>
+        <v>580.982</v>
       </c>
       <c r="H8" t="n">
-        <v>544.047</v>
+        <v>1280</v>
       </c>
       <c r="I8" t="n">
-        <v>242.538</v>
+        <v>451.571</v>
       </c>
       <c r="J8" t="n">
-        <v>77.408</v>
+        <v>49.385</v>
       </c>
       <c r="K8" t="n">
-        <v>469.1894</v>
+        <v>1237.4009</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1087,31 +1087,31 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>286.635</v>
+        <v>573.269</v>
       </c>
       <c r="N8" t="n">
-        <v>575.169</v>
+        <v>1150.339</v>
       </c>
       <c r="O8" t="n">
-        <v>230.772</v>
+        <v>461.545</v>
       </c>
       <c r="P8" t="n">
-        <v>92.702</v>
+        <v>185.404</v>
       </c>
       <c r="Q8" t="n">
-        <v>485.6909</v>
+        <v>971.3817</v>
       </c>
       <c r="R8" t="n">
-        <v>31.483</v>
+        <v>129.89</v>
       </c>
       <c r="S8" t="n">
-        <v>19.295</v>
+        <v>136.384</v>
       </c>
       <c r="T8" t="n">
-        <v>-16.5014</v>
+        <v>266.0192</v>
       </c>
       <c r="U8" t="n">
-        <v>3.398</v>
+        <v>27.386</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1132,38 +1132,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>008_jpg.rf.5812b75fe38ce91b0ecc6190e59be8c3.jpg</t>
+          <t>008_jpg.rf.f23554dcb86c2b7e7aacab563ef7372b.jpg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8675</v>
+        <v>0.8763</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9318</v>
+        <v>0.9908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>299.976</v>
+        <v>630.374</v>
       </c>
       <c r="H9" t="n">
-        <v>533.7430000000001</v>
+        <v>1004.223</v>
       </c>
       <c r="I9" t="n">
-        <v>297.505</v>
+        <v>604.7910000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>157.135</v>
+        <v>329.953</v>
       </c>
       <c r="K9" t="n">
-        <v>376.6158</v>
+        <v>674.7556</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1171,31 +1171,31 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>315.426</v>
+        <v>630.851</v>
       </c>
       <c r="N9" t="n">
-        <v>537.319</v>
+        <v>1074.638</v>
       </c>
       <c r="O9" t="n">
-        <v>283.927</v>
+        <v>567.853</v>
       </c>
       <c r="P9" t="n">
-        <v>175.517</v>
+        <v>351.033</v>
       </c>
       <c r="Q9" t="n">
-        <v>363.171</v>
+        <v>726.3421</v>
       </c>
       <c r="R9" t="n">
-        <v>15.859</v>
+        <v>70.417</v>
       </c>
       <c r="S9" t="n">
-        <v>22.853</v>
+        <v>42.53</v>
       </c>
       <c r="T9" t="n">
-        <v>13.4448</v>
+        <v>-51.5864</v>
       </c>
       <c r="U9" t="n">
-        <v>3.702</v>
+        <v>7.102</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1216,38 +1216,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>009_jpg.rf.8bab93b7d56749aa98648bdd1ca7afdb.jpg</t>
+          <t>009_jpg.rf.e33db8a91463e24851d4d7a6897d4b71.jpg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.865</v>
+        <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>0.799</v>
+        <v>0.4674</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8479</v>
+        <v>0.7326</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9577</v>
+        <v>0.9379</v>
       </c>
       <c r="G10" t="n">
-        <v>347.493</v>
+        <v>649.3200000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>540.101</v>
+        <v>1151.51</v>
       </c>
       <c r="I10" t="n">
-        <v>387.522</v>
+        <v>715.626</v>
       </c>
       <c r="J10" t="n">
-        <v>235.976</v>
+        <v>420.457</v>
       </c>
       <c r="K10" t="n">
-        <v>306.7483</v>
+        <v>734.0536</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>321.671</v>
+        <v>642.342</v>
       </c>
       <c r="N10" t="n">
-        <v>617.698</v>
+        <v>1235.396</v>
       </c>
       <c r="O10" t="n">
-        <v>367.094</v>
+        <v>733.189</v>
       </c>
       <c r="P10" t="n">
-        <v>215.782</v>
+        <v>431.565</v>
       </c>
       <c r="Q10" t="n">
-        <v>404.474</v>
+        <v>808.9479</v>
       </c>
       <c r="R10" t="n">
-        <v>81.78</v>
+        <v>84.175</v>
       </c>
       <c r="S10" t="n">
-        <v>28.724</v>
+        <v>20.78</v>
       </c>
       <c r="T10" t="n">
-        <v>-97.7257</v>
+        <v>-74.8943</v>
       </c>
       <c r="U10" t="n">
-        <v>24.161</v>
+        <v>9.257999999999999</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1300,38 +1300,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>010_jpg.rf.548a6fc07e0dd15ce1fb1c2efc5af9fa.jpg</t>
+          <t>010_jpg.rf.e0c6d70754837121670c4e801b233d42.jpg</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8768</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9382</v>
+        <v>0.982</v>
       </c>
       <c r="F11" t="n">
-        <v>0.919</v>
+        <v>0.99</v>
       </c>
       <c r="G11" t="n">
-        <v>206.573</v>
+        <v>386.008</v>
       </c>
       <c r="H11" t="n">
-        <v>139.831</v>
+        <v>301.168</v>
       </c>
       <c r="I11" t="n">
-        <v>223.9</v>
+        <v>501.952</v>
       </c>
       <c r="J11" t="n">
-        <v>445.839</v>
+        <v>887.705</v>
       </c>
       <c r="K11" t="n">
-        <v>306.4985</v>
+        <v>597.8868</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1339,31 +1339,31 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>193.721</v>
+        <v>387.443</v>
       </c>
       <c r="N11" t="n">
-        <v>142.822</v>
+        <v>285.645</v>
       </c>
       <c r="O11" t="n">
-        <v>240.371</v>
+        <v>480.742</v>
       </c>
       <c r="P11" t="n">
-        <v>427.916</v>
+        <v>855.831</v>
       </c>
       <c r="Q11" t="n">
-        <v>288.8845</v>
+        <v>577.769</v>
       </c>
       <c r="R11" t="n">
-        <v>13.195</v>
+        <v>15.589</v>
       </c>
       <c r="S11" t="n">
-        <v>24.343</v>
+        <v>38.286</v>
       </c>
       <c r="T11" t="n">
-        <v>17.6139</v>
+        <v>20.1178</v>
       </c>
       <c r="U11" t="n">
-        <v>6.097</v>
+        <v>3.482</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011_jpg.rf.31dfe6cf21e941713e13d48e451b5b34.jpg</t>
+          <t>011_jpg.rf.35842d49ed63fff87cb5a0667af46aee.jpg</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.853</v>
+        <v>0.844</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.849</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8454</v>
+        <v>0.9486</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9688</v>
+        <v>0.977</v>
       </c>
       <c r="G12" t="n">
-        <v>313.464</v>
+        <v>648.551</v>
       </c>
       <c r="H12" t="n">
-        <v>555.908</v>
+        <v>1280</v>
       </c>
       <c r="I12" t="n">
-        <v>288.555</v>
+        <v>531.779</v>
       </c>
       <c r="J12" t="n">
-        <v>158.752</v>
+        <v>180.315</v>
       </c>
       <c r="K12" t="n">
-        <v>397.937</v>
+        <v>1105.8672</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1423,31 +1423,31 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>321.337</v>
+        <v>642.674</v>
       </c>
       <c r="N12" t="n">
-        <v>600.563</v>
+        <v>1201.125</v>
       </c>
       <c r="O12" t="n">
-        <v>265.475</v>
+        <v>530.949</v>
       </c>
       <c r="P12" t="n">
-        <v>130.791</v>
+        <v>261.583</v>
       </c>
       <c r="Q12" t="n">
-        <v>473.0808</v>
+        <v>946.1616</v>
       </c>
       <c r="R12" t="n">
-        <v>45.343</v>
+        <v>79.09399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>36.256</v>
+        <v>81.27200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-75.1438</v>
+        <v>159.7056</v>
       </c>
       <c r="U12" t="n">
-        <v>15.884</v>
+        <v>16.879</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012_jpg.rf.1c49f445f9a076103a044e4d7ec4cbba.jpg</t>
+          <t>012_jpg.rf.fa9837bd46cddb121cb377150a2cce3c.jpg</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1478,28 +1478,28 @@
         <v>0.894</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707</v>
+        <v>0.8743</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9396</v>
+        <v>0.9786</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9604</v>
+        <v>0.9505</v>
       </c>
       <c r="G13" t="n">
-        <v>478.133</v>
+        <v>934.008</v>
       </c>
       <c r="H13" t="n">
-        <v>571.754</v>
+        <v>1052.956</v>
       </c>
       <c r="I13" t="n">
-        <v>376.219</v>
+        <v>746.72</v>
       </c>
       <c r="J13" t="n">
-        <v>128.511</v>
+        <v>285.59</v>
       </c>
       <c r="K13" t="n">
-        <v>454.8081</v>
+        <v>789.8905</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>464.378</v>
+        <v>928.7569999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>553.162</v>
+        <v>1106.324</v>
       </c>
       <c r="O13" t="n">
-        <v>382.278</v>
+        <v>764.556</v>
       </c>
       <c r="P13" t="n">
-        <v>144.334</v>
+        <v>288.669</v>
       </c>
       <c r="Q13" t="n">
-        <v>416.9901</v>
+        <v>833.9801</v>
       </c>
       <c r="R13" t="n">
-        <v>23.126</v>
+        <v>53.627</v>
       </c>
       <c r="S13" t="n">
-        <v>16.944</v>
+        <v>18.099</v>
       </c>
       <c r="T13" t="n">
-        <v>37.818</v>
+        <v>-44.0896</v>
       </c>
       <c r="U13" t="n">
-        <v>9.069000000000001</v>
+        <v>5.287</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1552,38 +1552,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>013_jpg.rf.5aa0c8322ac4e403fc96ddf0b299a532.jpg</t>
+          <t>013_jpg.rf.8f21a62134923cd3bbdc500dc41d137b.jpg</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.923</v>
+        <v>0.926</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8683</v>
+        <v>0.8842</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9699</v>
+        <v>0.9754</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9764</v>
+        <v>0.9819</v>
       </c>
       <c r="G14" t="n">
-        <v>292.029</v>
+        <v>557.3339999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>575.604</v>
+        <v>1168.933</v>
       </c>
       <c r="I14" t="n">
-        <v>244.429</v>
+        <v>489.692</v>
       </c>
       <c r="J14" t="n">
-        <v>144.071</v>
+        <v>208.036</v>
       </c>
       <c r="K14" t="n">
-        <v>434.1496</v>
+        <v>963.2746</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1591,31 +1591,31 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>294.252</v>
+        <v>588.505</v>
       </c>
       <c r="N14" t="n">
-        <v>578.5549999999999</v>
+        <v>1157.111</v>
       </c>
       <c r="O14" t="n">
-        <v>257.857</v>
+        <v>515.7140000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>158.724</v>
+        <v>317.448</v>
       </c>
       <c r="Q14" t="n">
-        <v>421.4061</v>
+        <v>842.8121</v>
       </c>
       <c r="R14" t="n">
-        <v>3.695</v>
+        <v>33.337</v>
       </c>
       <c r="S14" t="n">
-        <v>19.875</v>
+        <v>112.463</v>
       </c>
       <c r="T14" t="n">
-        <v>12.7435</v>
+        <v>120.4624</v>
       </c>
       <c r="U14" t="n">
-        <v>3.024</v>
+        <v>14.293</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1636,38 +1636,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>014_jpg.rf.3c9e80b37f0a897edf939f5b2a539ad8.jpg</t>
+          <t>014_jpg.rf.0cfbd1a4d6ff4cd0ed4cb1bf7dfa9c7c.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.892</v>
+        <v>0.803</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8804</v>
+        <v>0.8898</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9224</v>
+        <v>0.9869</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9346</v>
+        <v>0.9921</v>
       </c>
       <c r="G15" t="n">
-        <v>287.137</v>
+        <v>566.173</v>
       </c>
       <c r="H15" t="n">
-        <v>33.056</v>
+        <v>64.55800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>328.459</v>
+        <v>699.977</v>
       </c>
       <c r="J15" t="n">
-        <v>394.89</v>
+        <v>836.307</v>
       </c>
       <c r="K15" t="n">
-        <v>364.1858</v>
+        <v>783.2628999999999</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1675,31 +1675,31 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>290.867</v>
+        <v>581.7329999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>24.141</v>
+        <v>48.281</v>
       </c>
       <c r="O15" t="n">
-        <v>343.343</v>
+        <v>686.687</v>
       </c>
       <c r="P15" t="n">
-        <v>388.954</v>
+        <v>777.908</v>
       </c>
       <c r="Q15" t="n">
-        <v>368.5682</v>
+        <v>737.1363</v>
       </c>
       <c r="R15" t="n">
-        <v>9.664</v>
+        <v>22.518</v>
       </c>
       <c r="S15" t="n">
-        <v>16.025</v>
+        <v>59.893</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.3824</v>
+        <v>46.1266</v>
       </c>
       <c r="U15" t="n">
-        <v>1.189</v>
+        <v>6.258</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015_jpg.rf.94b4a7961d4eac445d4907eb273a8c9c.jpg</t>
+          <t>015_jpg.rf.1b9223c5e1999af8d99344be30ca1561.jpg</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.887</v>
+        <v>0.867</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8491</v>
+        <v>0.8821</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9092</v>
+        <v>0.9805</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9303</v>
+        <v>0.9859</v>
       </c>
       <c r="G16" t="n">
-        <v>311.7</v>
+        <v>620.813</v>
       </c>
       <c r="H16" t="n">
-        <v>62.509</v>
+        <v>148.388</v>
       </c>
       <c r="I16" t="n">
-        <v>356.896</v>
+        <v>712.824</v>
       </c>
       <c r="J16" t="n">
-        <v>468.876</v>
+        <v>908.141</v>
       </c>
       <c r="K16" t="n">
-        <v>408.873</v>
+        <v>765.3042</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1759,31 +1759,31 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>306.948</v>
+        <v>613.896</v>
       </c>
       <c r="N16" t="n">
-        <v>72.387</v>
+        <v>144.775</v>
       </c>
       <c r="O16" t="n">
-        <v>348.422</v>
+        <v>696.8440000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>459.208</v>
+        <v>918.4160000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>389.0375</v>
+        <v>778.075</v>
       </c>
       <c r="R16" t="n">
-        <v>10.962</v>
+        <v>7.804</v>
       </c>
       <c r="S16" t="n">
-        <v>12.857</v>
+        <v>18.999</v>
       </c>
       <c r="T16" t="n">
-        <v>19.8355</v>
+        <v>-12.7708</v>
       </c>
       <c r="U16" t="n">
-        <v>5.099</v>
+        <v>1.641</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1804,38 +1804,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>016_jpg.rf.7ab63b1fd0e68335acee897bc3b0a865.jpg</t>
+          <t>016_jpg.rf.5ecdd09f5a9abb3d2d7684c020bc3a7c.jpg</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.767</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8524</v>
+        <v>0.876</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8884</v>
+        <v>0.9671</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9425</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>342.553</v>
+        <v>635.66</v>
       </c>
       <c r="H17" t="n">
-        <v>123.661</v>
+        <v>266.979</v>
       </c>
       <c r="I17" t="n">
-        <v>369.001</v>
+        <v>766.021</v>
       </c>
       <c r="J17" t="n">
-        <v>485.424</v>
+        <v>971.862</v>
       </c>
       <c r="K17" t="n">
-        <v>362.7285</v>
+        <v>716.8362</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1843,31 +1843,31 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>336.483</v>
+        <v>671.966</v>
       </c>
       <c r="N17" t="n">
-        <v>134.807</v>
+        <v>269.614</v>
       </c>
       <c r="O17" t="n">
-        <v>379.931</v>
+        <v>758.8630000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>483.397</v>
+        <v>966.794</v>
       </c>
       <c r="Q17" t="n">
-        <v>351.2872</v>
+        <v>702.5744</v>
       </c>
       <c r="R17" t="n">
-        <v>12.692</v>
+        <v>36.402</v>
       </c>
       <c r="S17" t="n">
-        <v>11.117</v>
+        <v>8.771000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>11.4413</v>
+        <v>14.2618</v>
       </c>
       <c r="U17" t="n">
-        <v>3.257</v>
+        <v>2.03</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1888,38 +1888,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>017_jpg.rf.f41244d846f5acefd512d3fe33b1f7c7.jpg</t>
+          <t>017_jpg.rf.800e6e6a06af29ed0cd644c289f5590b.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.859</v>
+        <v>0.871</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8497</v>
+        <v>0.8398</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9397</v>
+        <v>0.9853</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9737</v>
+        <v>0.9881</v>
       </c>
       <c r="G18" t="n">
-        <v>211.107</v>
+        <v>464.693</v>
       </c>
       <c r="H18" t="n">
-        <v>600.188</v>
+        <v>1257.139</v>
       </c>
       <c r="I18" t="n">
-        <v>235.609</v>
+        <v>480.995</v>
       </c>
       <c r="J18" t="n">
-        <v>108.494</v>
+        <v>231.038</v>
       </c>
       <c r="K18" t="n">
-        <v>492.304</v>
+        <v>1026.2309</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1927,31 +1927,31 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>237.736</v>
+        <v>474.473</v>
       </c>
       <c r="N18" t="n">
-        <v>595.973</v>
+        <v>1191.945</v>
       </c>
       <c r="O18" t="n">
-        <v>220.949</v>
+        <v>440.899</v>
       </c>
       <c r="P18" t="n">
-        <v>127.894</v>
+        <v>255.789</v>
       </c>
       <c r="Q18" t="n">
-        <v>468.3791</v>
+        <v>936.7583</v>
       </c>
       <c r="R18" t="n">
-        <v>26.961</v>
+        <v>65.92400000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>24.316</v>
+        <v>47.12</v>
       </c>
       <c r="T18" t="n">
-        <v>23.9248</v>
+        <v>89.4727</v>
       </c>
       <c r="U18" t="n">
-        <v>5.108</v>
+        <v>9.551</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1972,38 +1972,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>018_jpg.rf.22c1355b4bd4dc78157bf7cb3b88bd48.jpg</t>
+          <t>018_jpg.rf.4e757b98688bd1347c4bad7ee090ce17.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.884</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9548</v>
+        <v>0.9879</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9851</v>
+        <v>0.9747</v>
       </c>
       <c r="G19" t="n">
-        <v>348.179</v>
+        <v>694.254</v>
       </c>
       <c r="H19" t="n">
-        <v>579.057</v>
+        <v>1173.445</v>
       </c>
       <c r="I19" t="n">
-        <v>282.419</v>
+        <v>580.131</v>
       </c>
       <c r="J19" t="n">
-        <v>192.392</v>
+        <v>322.759</v>
       </c>
       <c r="K19" t="n">
-        <v>392.2171</v>
+        <v>858.3071</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2011,31 +2011,31 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>344.19</v>
+        <v>688.38</v>
       </c>
       <c r="N19" t="n">
-        <v>607.3339999999999</v>
+        <v>1214.668</v>
       </c>
       <c r="O19" t="n">
-        <v>303.563</v>
+        <v>607.125</v>
       </c>
       <c r="P19" t="n">
-        <v>190.888</v>
+        <v>381.777</v>
       </c>
       <c r="Q19" t="n">
-        <v>418.4228</v>
+        <v>836.8456</v>
       </c>
       <c r="R19" t="n">
-        <v>28.557</v>
+        <v>41.639</v>
       </c>
       <c r="S19" t="n">
-        <v>21.197</v>
+        <v>64.898</v>
       </c>
       <c r="T19" t="n">
-        <v>-26.2057</v>
+        <v>21.4615</v>
       </c>
       <c r="U19" t="n">
-        <v>6.263</v>
+        <v>2.565</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2056,38 +2056,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>019_jpg.rf.5b1215807086f746eeb6c3f30bedcbee.jpg</t>
+          <t>019_jpg.rf.7e8dc2ab66db10dc776833fa9ef6fc0d.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.955</v>
+        <v>0.888</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8496</v>
+        <v>0.8319</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8499</v>
+        <v>0.9657</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9499</v>
+        <v>0.9885</v>
       </c>
       <c r="G20" t="n">
-        <v>384.566</v>
+        <v>814.8200000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>624.977</v>
+        <v>1280</v>
       </c>
       <c r="I20" t="n">
-        <v>419.606</v>
+        <v>776.682</v>
       </c>
       <c r="J20" t="n">
-        <v>127.871</v>
+        <v>132.55</v>
       </c>
       <c r="K20" t="n">
-        <v>498.3403</v>
+        <v>1148.0837</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2095,31 +2095,31 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>380.585</v>
+        <v>761.17</v>
       </c>
       <c r="N20" t="n">
-        <v>608.1799999999999</v>
+        <v>1216.361</v>
       </c>
       <c r="O20" t="n">
-        <v>411.055</v>
+        <v>822.111</v>
       </c>
       <c r="P20" t="n">
-        <v>135.87</v>
+        <v>271.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>473.2923</v>
+        <v>946.5845</v>
       </c>
       <c r="R20" t="n">
-        <v>17.262</v>
+        <v>83.236</v>
       </c>
       <c r="S20" t="n">
-        <v>11.709</v>
+        <v>146.416</v>
       </c>
       <c r="T20" t="n">
-        <v>25.048</v>
+        <v>201.4992</v>
       </c>
       <c r="U20" t="n">
-        <v>5.292</v>
+        <v>21.287</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2140,38 +2140,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>020_jpg.rf.6f3df25507befe53cc2fe1e6839d320a.jpg</t>
+          <t>020_jpg.rf.1f9fb195643b70333ad9d63ad77ffeec.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8592</v>
+        <v>0.8865</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9459</v>
+        <v>0.9888</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9856</v>
+        <v>0.9738</v>
       </c>
       <c r="G21" t="n">
-        <v>241.273</v>
+        <v>487.76</v>
       </c>
       <c r="H21" t="n">
-        <v>589.471</v>
+        <v>1143.36</v>
       </c>
       <c r="I21" t="n">
-        <v>229.336</v>
+        <v>499.209</v>
       </c>
       <c r="J21" t="n">
-        <v>230.985</v>
+        <v>520.2670000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>358.6852</v>
+        <v>623.1977000000001</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2179,31 +2179,31 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>237.877</v>
+        <v>475.754</v>
       </c>
       <c r="N21" t="n">
-        <v>590.05</v>
+        <v>1180.1</v>
       </c>
       <c r="O21" t="n">
-        <v>234.264</v>
+        <v>468.527</v>
       </c>
       <c r="P21" t="n">
-        <v>256.682</v>
+        <v>513.364</v>
       </c>
       <c r="Q21" t="n">
-        <v>333.3879</v>
+        <v>666.7757</v>
       </c>
       <c r="R21" t="n">
-        <v>3.445</v>
+        <v>38.652</v>
       </c>
       <c r="S21" t="n">
-        <v>26.165</v>
+        <v>31.449</v>
       </c>
       <c r="T21" t="n">
-        <v>25.2973</v>
+        <v>-43.578</v>
       </c>
       <c r="U21" t="n">
-        <v>7.588</v>
+        <v>6.536</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2224,38 +2224,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>021_jpg.rf.8b63d0945baeef56e60cbc002150e4bb.jpg</t>
+          <t>021_jpg.rf.e30b2c65f4d2d972f9dc3e3f715a546b.jpg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0.902</v>
+        <v>0.877</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8582</v>
+        <v>0.8728</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8235</v>
+        <v>0.9911</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9691</v>
+        <v>0.985</v>
       </c>
       <c r="G22" t="n">
-        <v>329.851</v>
+        <v>639.518</v>
       </c>
       <c r="H22" t="n">
-        <v>640</v>
+        <v>1263.7</v>
       </c>
       <c r="I22" t="n">
-        <v>311.189</v>
+        <v>667.857</v>
       </c>
       <c r="J22" t="n">
-        <v>188.235</v>
+        <v>422.63</v>
       </c>
       <c r="K22" t="n">
-        <v>452.1506</v>
+        <v>841.5465</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2263,31 +2263,31 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>337.419</v>
+        <v>674.837</v>
       </c>
       <c r="N22" t="n">
-        <v>620.877</v>
+        <v>1241.754</v>
       </c>
       <c r="O22" t="n">
-        <v>325.569</v>
+        <v>651.138</v>
       </c>
       <c r="P22" t="n">
-        <v>228.131</v>
+        <v>456.263</v>
       </c>
       <c r="Q22" t="n">
-        <v>392.9243</v>
+        <v>785.8484999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>20.566</v>
+        <v>41.582</v>
       </c>
       <c r="S22" t="n">
-        <v>42.409</v>
+        <v>37.559</v>
       </c>
       <c r="T22" t="n">
-        <v>59.2263</v>
+        <v>55.698</v>
       </c>
       <c r="U22" t="n">
-        <v>15.073</v>
+        <v>7.088</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>022_jpg.rf.116af67b6e3794e3f8ed2f5d51cca8a1.jpg</t>
+          <t>022_jpg.rf.e01e79cad2e3ad7f2ccf081146da4e27.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2318,28 +2318,28 @@
         <v>0.86</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8387</v>
+        <v>0.9036</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8994</v>
+        <v>0.9905</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9686</v>
+        <v>0.9865</v>
       </c>
       <c r="G23" t="n">
-        <v>233.206</v>
+        <v>490.069</v>
       </c>
       <c r="H23" t="n">
-        <v>618.697</v>
+        <v>1236.108</v>
       </c>
       <c r="I23" t="n">
-        <v>253.819</v>
+        <v>529.687</v>
       </c>
       <c r="J23" t="n">
-        <v>160.612</v>
+        <v>313.714</v>
       </c>
       <c r="K23" t="n">
-        <v>458.548</v>
+        <v>923.245</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2347,31 +2347,31 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>243.468</v>
+        <v>486.937</v>
       </c>
       <c r="N23" t="n">
-        <v>611.566</v>
+        <v>1223.132</v>
       </c>
       <c r="O23" t="n">
-        <v>251.086</v>
+        <v>502.172</v>
       </c>
       <c r="P23" t="n">
-        <v>180.731</v>
+        <v>361.462</v>
       </c>
       <c r="Q23" t="n">
-        <v>430.9025</v>
+        <v>861.8049999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>12.496</v>
+        <v>13.349</v>
       </c>
       <c r="S23" t="n">
-        <v>20.304</v>
+        <v>55.109</v>
       </c>
       <c r="T23" t="n">
-        <v>27.6455</v>
+        <v>61.4401</v>
       </c>
       <c r="U23" t="n">
-        <v>6.416</v>
+        <v>7.129</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2392,38 +2392,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>023_jpg.rf.c81eb814a1c67711193aa6d0ef2ba449.jpg</t>
+          <t>023_jpg.rf.fe1db156970b53ad9c41c422d68a6218.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.893</v>
+        <v>0.892</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8611</v>
+        <v>0.884</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9306</v>
+        <v>0.9837</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9611</v>
+        <v>0.9867</v>
       </c>
       <c r="G24" t="n">
-        <v>282.585</v>
+        <v>584.312</v>
       </c>
       <c r="H24" t="n">
-        <v>607.485</v>
+        <v>1171.48</v>
       </c>
       <c r="I24" t="n">
-        <v>289.596</v>
+        <v>588.886</v>
       </c>
       <c r="J24" t="n">
-        <v>218.839</v>
+        <v>422.358</v>
       </c>
       <c r="K24" t="n">
-        <v>388.7087</v>
+        <v>749.1353</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2431,31 +2431,31 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>289.174</v>
+        <v>578.348</v>
       </c>
       <c r="N24" t="n">
-        <v>599.716</v>
+        <v>1199.432</v>
       </c>
       <c r="O24" t="n">
-        <v>308.641</v>
+        <v>617.282</v>
       </c>
       <c r="P24" t="n">
-        <v>239.135</v>
+        <v>478.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>361.1062</v>
+        <v>722.2124</v>
       </c>
       <c r="R24" t="n">
-        <v>10.186</v>
+        <v>28.582</v>
       </c>
       <c r="S24" t="n">
-        <v>27.832</v>
+        <v>62.709</v>
       </c>
       <c r="T24" t="n">
-        <v>27.6025</v>
+        <v>26.923</v>
       </c>
       <c r="U24" t="n">
-        <v>7.644</v>
+        <v>3.728</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2476,38 +2476,38 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>024_jpg.rf.32a9c8afc84e54eb0a5df0b4c0ce394c.jpg</t>
+          <t>024_jpg.rf.ae35979c01561a7f0106f74bec6eafcb.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>0.827</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8646</v>
+        <v>0.9015</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9604</v>
+        <v>0.9866</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9732</v>
+        <v>0.9866</v>
       </c>
       <c r="G25" t="n">
-        <v>446.34</v>
+        <v>886.575</v>
       </c>
       <c r="H25" t="n">
-        <v>533.88</v>
+        <v>1153.169</v>
       </c>
       <c r="I25" t="n">
-        <v>420.064</v>
+        <v>846.8920000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>221.963</v>
+        <v>387.088</v>
       </c>
       <c r="K25" t="n">
-        <v>313.0214</v>
+        <v>767.1081</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2515,31 +2515,31 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>462.686</v>
+        <v>925.371</v>
       </c>
       <c r="N25" t="n">
-        <v>570.091</v>
+        <v>1140.182</v>
       </c>
       <c r="O25" t="n">
-        <v>402.591</v>
+        <v>805.183</v>
       </c>
       <c r="P25" t="n">
-        <v>212.896</v>
+        <v>425.791</v>
       </c>
       <c r="Q25" t="n">
-        <v>362.2152</v>
+        <v>724.4303</v>
       </c>
       <c r="R25" t="n">
-        <v>39.729</v>
+        <v>40.912</v>
       </c>
       <c r="S25" t="n">
-        <v>19.685</v>
+        <v>56.9</v>
       </c>
       <c r="T25" t="n">
-        <v>-49.1938</v>
+        <v>42.6778</v>
       </c>
       <c r="U25" t="n">
-        <v>13.581</v>
+        <v>5.891</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2560,38 +2560,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>025_jpg.rf.f06a8c53e7f4b681c9427183b37f5bc2.jpg</t>
+          <t>025_jpg.rf.4d671849dfc80903ecd921d75682b604.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>0.954</v>
+        <v>0.88</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6907</v>
+        <v>0.8651</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8888</v>
+        <v>0.9647</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8989</v>
+        <v>0.963</v>
       </c>
       <c r="G26" t="n">
-        <v>190.105</v>
+        <v>355.812</v>
       </c>
       <c r="H26" t="n">
-        <v>124.498</v>
+        <v>275.79</v>
       </c>
       <c r="I26" t="n">
-        <v>254.43</v>
+        <v>587.658</v>
       </c>
       <c r="J26" t="n">
-        <v>515.728</v>
+        <v>1025.113</v>
       </c>
       <c r="K26" t="n">
-        <v>396.4838</v>
+        <v>784.3711</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2599,31 +2599,31 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>170.678</v>
+        <v>341.356</v>
       </c>
       <c r="N26" t="n">
-        <v>157.031</v>
+        <v>314.062</v>
       </c>
       <c r="O26" t="n">
-        <v>284.942</v>
+        <v>569.884</v>
       </c>
       <c r="P26" t="n">
-        <v>519.3049999999999</v>
+        <v>1038.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>379.8666</v>
+        <v>759.7333</v>
       </c>
       <c r="R26" t="n">
-        <v>37.892</v>
+        <v>40.911</v>
       </c>
       <c r="S26" t="n">
-        <v>30.72</v>
+        <v>22.318</v>
       </c>
       <c r="T26" t="n">
-        <v>16.6171</v>
+        <v>24.6379</v>
       </c>
       <c r="U26" t="n">
-        <v>4.374</v>
+        <v>3.243</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2644,38 +2644,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>026_jpg.rf.997b35ef0b16674048632d1fe4f74d00.jpg</t>
+          <t>026_jpg.rf.033a01a968e2d80a5eb6f6ceeafcdaf7.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.913</v>
+        <v>0.887</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9136</v>
+        <v>0.9817</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9573</v>
+        <v>0.9792</v>
       </c>
       <c r="G27" t="n">
-        <v>397.925</v>
+        <v>769.102</v>
       </c>
       <c r="H27" t="n">
-        <v>554.6950000000001</v>
+        <v>1048.651</v>
       </c>
       <c r="I27" t="n">
-        <v>338.953</v>
+        <v>653.1559999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>109.897</v>
+        <v>201.101</v>
       </c>
       <c r="K27" t="n">
-        <v>448.6905</v>
+        <v>855.4444</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2683,31 +2683,31 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>373.814</v>
+        <v>747.628</v>
       </c>
       <c r="N27" t="n">
-        <v>556.548</v>
+        <v>1113.096</v>
       </c>
       <c r="O27" t="n">
-        <v>315.412</v>
+        <v>630.824</v>
       </c>
       <c r="P27" t="n">
-        <v>131.638</v>
+        <v>263.276</v>
       </c>
       <c r="Q27" t="n">
-        <v>428.9048</v>
+        <v>857.8096</v>
       </c>
       <c r="R27" t="n">
-        <v>24.182</v>
+        <v>67.929</v>
       </c>
       <c r="S27" t="n">
-        <v>32.044</v>
+        <v>66.06399999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>19.7857</v>
+        <v>-2.3652</v>
       </c>
       <c r="U27" t="n">
-        <v>4.613</v>
+        <v>0.276</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2728,38 +2728,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>027_jpg.rf.bef5c4b7ae4115dbc519047689c1b85a.jpg</t>
+          <t>027_jpg.rf.72419ebb26d8c503efe00763a9c30d9c.jpg</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.904</v>
+        <v>0.856</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8505</v>
+        <v>0.8767</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8173</v>
+        <v>0.9472</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9624</v>
+        <v>0.9782</v>
       </c>
       <c r="G28" t="n">
-        <v>225.984</v>
+        <v>487.414</v>
       </c>
       <c r="H28" t="n">
-        <v>586.735</v>
+        <v>1164.56</v>
       </c>
       <c r="I28" t="n">
-        <v>245.488</v>
+        <v>516.458</v>
       </c>
       <c r="J28" t="n">
-        <v>186.403</v>
+        <v>388.734</v>
       </c>
       <c r="K28" t="n">
-        <v>400.8063</v>
+        <v>776.3696</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2767,31 +2767,31 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>244.315</v>
+        <v>488.629</v>
       </c>
       <c r="N28" t="n">
-        <v>585.327</v>
+        <v>1170.653</v>
       </c>
       <c r="O28" t="n">
-        <v>235.004</v>
+        <v>470.009</v>
       </c>
       <c r="P28" t="n">
-        <v>184.117</v>
+        <v>368.234</v>
       </c>
       <c r="Q28" t="n">
-        <v>401.3179</v>
+        <v>802.6359</v>
       </c>
       <c r="R28" t="n">
-        <v>18.385</v>
+        <v>6.213</v>
       </c>
       <c r="S28" t="n">
-        <v>10.73</v>
+        <v>50.772</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-26.2663</v>
       </c>
       <c r="U28" t="n">
-        <v>0.127</v>
+        <v>3.272</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2812,38 +2812,38 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>028_jpg.rf.9dc294ecb02a107d9bb666dcad46368b.jpg</t>
+          <t>028_jpg.rf.09e34e1f2d036ef54156a0ab66e1068e.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.92</v>
+        <v>0.907</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8623</v>
+        <v>0.9054</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9326</v>
+        <v>0.9909</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9665</v>
+        <v>0.9717</v>
       </c>
       <c r="G29" t="n">
-        <v>383.225</v>
+        <v>793.628</v>
       </c>
       <c r="H29" t="n">
-        <v>632.554</v>
+        <v>1181.156</v>
       </c>
       <c r="I29" t="n">
-        <v>374.963</v>
+        <v>766.4640000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>154.635</v>
+        <v>410.051</v>
       </c>
       <c r="K29" t="n">
-        <v>477.9907</v>
+        <v>771.5839</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2851,31 +2851,31 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>394.974</v>
+        <v>789.947</v>
       </c>
       <c r="N29" t="n">
-        <v>624.263</v>
+        <v>1248.525</v>
       </c>
       <c r="O29" t="n">
-        <v>405.131</v>
+        <v>810.261</v>
       </c>
       <c r="P29" t="n">
-        <v>200.199</v>
+        <v>400.398</v>
       </c>
       <c r="Q29" t="n">
-        <v>424.1853</v>
+        <v>848.3706</v>
       </c>
       <c r="R29" t="n">
-        <v>14.38</v>
+        <v>67.46899999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>54.646</v>
+        <v>44.848</v>
       </c>
       <c r="T29" t="n">
-        <v>53.8054</v>
+        <v>-76.7867</v>
       </c>
       <c r="U29" t="n">
-        <v>12.684</v>
+        <v>9.051</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2896,38 +2896,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>029_jpg.rf.68aa50dedf23782d475ba73aeefa8402.jpg</t>
+          <t>029_jpg.rf.bbd4c02a08752a88ec42e98dfd0b887c.jpg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8517</v>
+        <v>0.8821</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9675</v>
+        <v>0.9768</v>
       </c>
       <c r="G30" t="n">
-        <v>246.698</v>
+        <v>510.343</v>
       </c>
       <c r="H30" t="n">
-        <v>565.184</v>
+        <v>1113.864</v>
       </c>
       <c r="I30" t="n">
-        <v>268.313</v>
+        <v>541.433</v>
       </c>
       <c r="J30" t="n">
-        <v>228.569</v>
+        <v>481.263</v>
       </c>
       <c r="K30" t="n">
-        <v>337.3087</v>
+        <v>633.3644</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>244.994</v>
+        <v>489.988</v>
       </c>
       <c r="N30" t="n">
-        <v>573.33</v>
+        <v>1146.66</v>
       </c>
       <c r="O30" t="n">
-        <v>260.027</v>
+        <v>520.054</v>
       </c>
       <c r="P30" t="n">
-        <v>240.82</v>
+        <v>481.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>332.8494</v>
+        <v>665.6988</v>
       </c>
       <c r="R30" t="n">
-        <v>8.321999999999999</v>
+        <v>38.599</v>
       </c>
       <c r="S30" t="n">
-        <v>14.79</v>
+        <v>21.382</v>
       </c>
       <c r="T30" t="n">
-        <v>4.4593</v>
+        <v>-32.3345</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>4.857</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2980,38 +2980,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>030_jpg.rf.324003241288b34853323a8b697e5754.jpg</t>
+          <t>030_jpg.rf.c85444952d482cff241717c46e61d48b.jpg</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.867</v>
+        <v>0.944</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8464</v>
+        <v>0.8788</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9316</v>
+        <v>0.9775</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9659</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>334.507</v>
+        <v>690.491</v>
       </c>
       <c r="H31" t="n">
-        <v>554.665</v>
+        <v>1126.275</v>
       </c>
       <c r="I31" t="n">
-        <v>326.385</v>
+        <v>642.843</v>
       </c>
       <c r="J31" t="n">
-        <v>121.611</v>
+        <v>206.409</v>
       </c>
       <c r="K31" t="n">
-        <v>433.1301</v>
+        <v>921.0988</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3019,31 +3019,31 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>335.726</v>
+        <v>671.452</v>
       </c>
       <c r="N31" t="n">
-        <v>559.934</v>
+        <v>1119.867</v>
       </c>
       <c r="O31" t="n">
-        <v>316.259</v>
+        <v>632.5170000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>131.638</v>
+        <v>263.276</v>
       </c>
       <c r="Q31" t="n">
-        <v>428.738</v>
+        <v>857.476</v>
       </c>
       <c r="R31" t="n">
-        <v>5.408</v>
+        <v>20.089</v>
       </c>
       <c r="S31" t="n">
-        <v>14.251</v>
+        <v>57.796</v>
       </c>
       <c r="T31" t="n">
-        <v>4.3922</v>
+        <v>63.6228</v>
       </c>
       <c r="U31" t="n">
-        <v>1.024</v>
+        <v>7.42</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3064,38 +3064,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>031_jpg.rf.81b158711b26da9baabc14f9d9de3b5a.jpg</t>
+          <t>031_jpg.rf.ed77298eff2b9cd697e4d7c1c1d840c2.jpg</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8448</v>
+        <v>0.9011</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9516</v>
+        <v>0.9838</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9804</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>380.065</v>
+        <v>785.351</v>
       </c>
       <c r="H32" t="n">
-        <v>585.564</v>
+        <v>1147.208</v>
       </c>
       <c r="I32" t="n">
-        <v>358.227</v>
+        <v>749.037</v>
       </c>
       <c r="J32" t="n">
-        <v>201.794</v>
+        <v>391.307</v>
       </c>
       <c r="K32" t="n">
-        <v>384.3905</v>
+        <v>756.7719</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3103,31 +3103,31 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>388.819</v>
+        <v>776.6369999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>628.5599999999999</v>
+        <v>1257.121</v>
       </c>
       <c r="O32" t="n">
-        <v>381.906</v>
+        <v>762.813</v>
       </c>
       <c r="P32" t="n">
-        <v>202.945</v>
+        <v>405.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>425.6716</v>
+        <v>851.3431</v>
       </c>
       <c r="R32" t="n">
-        <v>43.878</v>
+        <v>110.258</v>
       </c>
       <c r="S32" t="n">
-        <v>23.707</v>
+        <v>20.06</v>
       </c>
       <c r="T32" t="n">
-        <v>-41.2811</v>
+        <v>-94.5712</v>
       </c>
       <c r="U32" t="n">
-        <v>9.698</v>
+        <v>11.108</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3148,38 +3148,38 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>032_jpg.rf.3d37a54c9ba12c154d2dfd85c178f1a5.jpg</t>
+          <t>032_jpg.rf.7479b7080b739ee37ff2a4e3533229cc.jpg</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>0.929</v>
+        <v>0.927</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.886</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9224</v>
+        <v>0.9287</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9898</v>
       </c>
       <c r="G33" t="n">
-        <v>211.898</v>
+        <v>444.429</v>
       </c>
       <c r="H33" t="n">
-        <v>595.903</v>
+        <v>1216.791</v>
       </c>
       <c r="I33" t="n">
-        <v>223.866</v>
+        <v>474.611</v>
       </c>
       <c r="J33" t="n">
-        <v>220.841</v>
+        <v>395.406</v>
       </c>
       <c r="K33" t="n">
-        <v>375.2534</v>
+        <v>821.9394</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3187,31 +3187,31 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>217</v>
+        <v>432.999</v>
       </c>
       <c r="N33" t="n">
-        <v>625.598</v>
+        <v>1251.196</v>
       </c>
       <c r="O33" t="n">
-        <v>236.749</v>
+        <v>472.498</v>
       </c>
       <c r="P33" t="n">
-        <v>205.907</v>
+        <v>411.815</v>
       </c>
       <c r="Q33" t="n">
-        <v>420.1548</v>
+        <v>840.3096</v>
       </c>
       <c r="R33" t="n">
-        <v>30.13</v>
+        <v>36.253</v>
       </c>
       <c r="S33" t="n">
-        <v>19.722</v>
+        <v>16.544</v>
       </c>
       <c r="T33" t="n">
-        <v>-44.9014</v>
+        <v>-18.3702</v>
       </c>
       <c r="U33" t="n">
-        <v>10.687</v>
+        <v>2.186</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3232,38 +3232,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>033_jpg.rf.f069be44f0966621607332c12f0c9ee6.jpg</t>
+          <t>033_jpg.rf.10565077269e8d1bdd2fbc43dd98a298.jpg</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.839</v>
+        <v>0.844</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8539</v>
+        <v>0.8456</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9665</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9821</v>
+        <v>0.9691</v>
       </c>
       <c r="G34" t="n">
-        <v>345.15</v>
+        <v>686.573</v>
       </c>
       <c r="H34" t="n">
-        <v>549.603</v>
+        <v>1192.802</v>
       </c>
       <c r="I34" t="n">
-        <v>281.329</v>
+        <v>541.636</v>
       </c>
       <c r="J34" t="n">
-        <v>183.822</v>
+        <v>239.755</v>
       </c>
       <c r="K34" t="n">
-        <v>371.3072</v>
+        <v>964.005</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3271,31 +3271,31 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>342.408</v>
+        <v>683.8150000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>589.0599999999999</v>
+        <v>1178.12</v>
       </c>
       <c r="O34" t="n">
-        <v>275.26</v>
+        <v>549.52</v>
       </c>
       <c r="P34" t="n">
-        <v>166.407</v>
+        <v>332.814</v>
       </c>
       <c r="Q34" t="n">
-        <v>427.9536</v>
+        <v>855.9073</v>
       </c>
       <c r="R34" t="n">
-        <v>39.552</v>
+        <v>14.938</v>
       </c>
       <c r="S34" t="n">
-        <v>18.442</v>
+        <v>93.393</v>
       </c>
       <c r="T34" t="n">
-        <v>-56.6464</v>
+        <v>108.0977</v>
       </c>
       <c r="U34" t="n">
-        <v>13.237</v>
+        <v>12.63</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.385</v>
+        <v>41.582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.304</v>
+        <v>47.12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.78</v>
+        <v>146.416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.7553</v>
+        <v>65.2286</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9739</v>
+        <v>30.3197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.036</v>
+        <v>7.647</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97.7257</v>
+        <v>266.0192</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.892</v>
+        <v>0.88</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3579,12 +3579,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33-all-test_enhanced/test/images</t>
+          <t>33-all-test_enhanced1280/test/images</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolo11_pose_run-batch4_重新標註/weights_ready.pt</t>
+          <t>yolo11_pose_run-batch4_重新標註1280/weights_ready.pt</t>
         </is>
       </c>
       <c r="C2" t="n">
